--- a/content/quiz_hint.xlsx
+++ b/content/quiz_hint.xlsx
@@ -10,6 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="읽는 법" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="초등" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="중등" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="연습" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -457,7 +458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B21"/>
+  <dimension ref="A1:B22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -580,7 +581,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>화면에서 물음 위에 먼저 뜨는 문장이다. 비어 있는 문항은 물음 한 줄만으로 선다(일곱 개).</t>
+          <t>화면에서 물음 위에 먼저 뜨는 문장이다. 38문항 모두 있다(비어 있던 일곱은 2026-09-26에 채웠다).</t>
         </is>
       </c>
     </row>
@@ -676,7 +677,19 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>연습 시트</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>튜토리얼 연습 판의 힌트 퀴즈 한 문제(G00-1). 초등(보기 셋)·중등(넷, 형조 더함)을 한 시트에 「학년」 열로 가른다. 📜 한국민족문화대백과 「육조」 — 병조 "군무(軍務) … 병갑(兵甲) · 기장(器仗) … 을 맡았다" (2026-09-23 🙋 "응 그렇게 하자.")</t>
         </is>
       </c>
     </row>
@@ -803,7 +816,11 @@
           <t>일화 41 「태종의 셋째 아들」</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr"/>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>세종은 할아버지 태조가 임금이던 때, 한양에서 태어났습니다. 아버지 태종이 아직 임금이 되기 전이었지요.</t>
+        </is>
+      </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
           <t>세종은 태종의 몇째 아들일까요?</t>
@@ -860,7 +877,11 @@
           <t>일화 42 「밤새워 글을 읽던 아이」</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr"/>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>태종은 신하들 앞에서 한 아들의 이름을 부르며 이렇게 칭찬했습니다. "몹시 춥고 더운 날에도 밤을 새워 글을 읽고, 나라에 큰일이 생길 때마다 남다른 의견을 낸다." 그 아들이 훗날의 세종이지요.</t>
+        </is>
+      </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
           <t>세종이 왕이 되기 전에 불리던 이름은 무엇일까요?</t>
@@ -917,7 +938,11 @@
           <t>일화 43 「근정전에서 왕이 되다」</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr"/>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>태종은 오랜 병을 이유로 세종에게 왕위를 물려주려 했습니다. 세종은 배움이 얕고 나이가 어리다며 여러 번 사양했지만 끝내 허락받지 못했지요. 즉위식 날 세종은 모든 신하의 축하 인사를 받고, 아버지를 상왕으로, 어머니를 대비로 높였습니다.</t>
+        </is>
+      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
           <t>세종이 즉위식을 치른 곳은 어디일까요?</t>
@@ -1157,7 +1182,11 @@
           <t>일화 32 「측우기라는 이름」</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr"/>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>세종 때 나라에서는 강수량을 측정하는 규칙을 정했습니다. 한양에서는 비가 온 뒤에 관원이 직접 빗물을 받는 기구에 고인 물의 깊이를 자로 재고, 비가 내린 시각과 그친 시각까지 적어서 임금에게 보고했지요. 지방 고을에서도 똑같이 하게 했습니다.</t>
+        </is>
+      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
           <t>세종 즉위 기간에 만들어진 발명품 중 강수량을 측정하기 위해 제작한 기구의 이름은 무엇일까요?</t>
@@ -1214,7 +1243,11 @@
           <t>일화 37 「눈병을 고치러 간 청주」</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr"/>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>어떤 사람이 세종에게 아뢰었습니다. "후추 맛이 나는 물이 있는데, 이름을 초수라 하고 온갖 병을 고칩니다." 세종은 그 물을 떠 온 사람에게 무명 열 필을 상으로 내리고, 그곳에 머무를 임시 궁궐을 짓게 했습니다.</t>
+        </is>
+      </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
           <t>세종이 눈병을 고치려고 왕비와 함께 내려가 여러 달 머문 고장은 어디일까요?</t>
@@ -1576,7 +1609,11 @@
           <t>새 일화 「세종대왕의 생일」</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr"/>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>세종은 백성 누구나 쉽게 배워 쓸 수 있도록 한글을 만들어 널리 펴냈습니다. 그래서 세종은 겨레의 큰 스승으로 꼽히고, 세종이 태어난 날은 스승의 날이 되었지요.</t>
+        </is>
+      </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
           <t>다음 중 세종의 생일은 언제일까요?</t>
@@ -1633,7 +1670,11 @@
           <t>새 일화 「세종대왕의 이름」</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr"/>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>유교 문화권에서는 임금과 같이 신분이 존귀한 사람의 이름을 직접 부르거나 글로 쓰지 않았는데, 이를 '휘'라고 했습니다. 세상을 떠난 사람이 살아서 쓰던 이름도 '휘'라고 불렀지요.</t>
+        </is>
+      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
           <t>세종의 이름은 무엇일까요?</t>
@@ -3195,7 +3236,11 @@
           <t>일화 41 「태종의 셋째 아들」</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr"/>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>세종은 할아버지 태조가 임금이던 때, 한양에서 태어났습니다. 아버지 태종이 아직 임금이 되기 전이었지요.</t>
+        </is>
+      </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
           <t>세종은 태종의 몇째 아들일까요?</t>
@@ -3257,7 +3302,11 @@
           <t>일화 42 「밤새워 글을 읽던 아이」</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr"/>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>태종은 신하들 앞에서 한 아들의 이름을 부르며 이렇게 칭찬했습니다. "몹시 춥고 더운 날에도 밤을 새워 글을 읽고, 나라에 큰일이 생길 때마다 남다른 의견을 낸다." 그 아들이 훗날의 세종이지요.</t>
+        </is>
+      </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
           <t>세종이 왕이 되기 전에 불리던 이름은 무엇일까요?</t>
@@ -3319,7 +3368,11 @@
           <t>일화 43 「근정전에서 왕이 되다」</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr"/>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>태종은 오랜 병을 이유로 세종에게 왕위를 물려주려 했습니다. 세종은 배움이 얕고 나이가 어리다며 여러 번 사양했지만 끝내 허락받지 못했지요. 즉위식 날 세종은 모든 신하의 축하 인사를 받고, 아버지를 상왕으로, 어머니를 대비로 높였습니다.</t>
+        </is>
+      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
           <t>세종이 즉위식을 치른 곳은 어디일까요?</t>
@@ -3579,7 +3632,11 @@
           <t>일화 32 「측우기라는 이름」</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr"/>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>세종 때 나라에서는 강수량을 측정하는 규칙을 정했습니다. 한양에서는 비가 온 뒤에 관원이 직접 빗물을 받는 기구에 고인 물의 깊이를 자로 재고, 비가 내린 시각과 그친 시각까지 적어서 임금에게 보고했지요. 지방 고을에서도 똑같이 하게 했습니다.</t>
+        </is>
+      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
           <t>세종 즉위 기간에 만들어진 발명품 중 강수량을 측정하기 위해 제작한 기구의 이름은 무엇일까요?</t>
@@ -3641,7 +3698,11 @@
           <t>일화 37 「눈병을 고치러 간 청주」</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr"/>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>어떤 사람이 세종에게 아뢰었습니다. "후추 맛이 나는 물이 있는데, 이름을 초수라 하고 온갖 병을 고칩니다." 세종은 그 물을 떠 온 사람에게 무명 열 필을 상으로 내리고, 그곳에 머무를 임시 궁궐을 짓게 했습니다.</t>
+        </is>
+      </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
           <t>세종이 눈병을 고치려고 왕비와 함께 내려가 여러 달 머문 고장은 어디일까요?</t>
@@ -4033,7 +4094,11 @@
           <t>새 일화 「세종대왕의 생일」</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr"/>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>세종은 백성 누구나 쉽게 배워 쓸 수 있도록 한글을 만들어 널리 펴냈습니다. 그래서 세종은 겨레의 큰 스승으로 꼽히고, 세종이 태어난 날은 스승의 날이 되었지요.</t>
+        </is>
+      </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
           <t>다음 중 세종의 생일은 언제일까요?</t>
@@ -4095,7 +4160,11 @@
           <t>새 일화 「세종대왕의 이름」</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr"/>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>유교 문화권에서는 임금과 같이 신분이 존귀한 사람의 이름을 직접 부르거나 글로 쓰지 않았는데, 이를 '휘'라고 했습니다. 세상을 떠난 사람이 살아서 쓰던 이름도 '휘'라고 불렀지요.</t>
+        </is>
+      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
           <t>세종의 이름은 무엇일까요?</t>
@@ -5645,6 +5714,262 @@
       <c r="N39" s="2" t="inlineStr">
         <is>
           <t>섞는다</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:O3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="6" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="6" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="6" max="6"/>
+    <col width="60" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="9" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>문항ID</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>문</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>빗장</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>조립 낱말</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>걸음</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>일화</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>일화 문장</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>물음</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>보기1</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>보기2</t>
+        </is>
+      </c>
+      <c r="K1" s="4" t="inlineStr">
+        <is>
+          <t>보기3</t>
+        </is>
+      </c>
+      <c r="L1" s="4" t="inlineStr">
+        <is>
+          <t>보기4</t>
+        </is>
+      </c>
+      <c r="M1" s="4" t="inlineStr">
+        <is>
+          <t>정답번호</t>
+        </is>
+      </c>
+      <c r="N1" s="4" t="inlineStr">
+        <is>
+          <t>보기 순서</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>학년</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>G00-1</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>육조거리(연습)</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>알현</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>연습 — 육조</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>세종이 임금이던 때, 광화문 앞에는 나랏일을 맡은 관청 여섯 곳이 있었습니다. 이 관청을 '조'라고 했고, 여섯 관청을 묶어 육조라고 불렀지요.</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>병사와 무기에 관한 일을 맡은 관청은 어디일까요?</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>병조</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>예조</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>호조</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>섞는다</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>초등</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>G00-1</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>육조거리(연습)</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>알현</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>연습 — 육조</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>세종이 임금이던 때, 광화문 앞에는 나랏일을 맡은 관청 여섯 곳이 있었습니다. 이 관청을 '조'라고 했고, 여섯 관청을 묶어 육조라고 불렀지요.</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>병사와 무기에 관한 일을 맡은 관청은 어디일까요?</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>병조</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>예조</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>호조</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>형조</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>섞는다</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>중등</t>
         </is>
       </c>
     </row>
